--- a/sample_questions.xlsx
+++ b/sample_questions.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1018,6 +1018,84 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>中国的首都是___，简称___。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>北京,北京市|京</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>北京简称京；判卷忽略大小写与首尾空格</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>编程基础</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>简述HTTP与HTTPS的主要区别。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HTTPS在HTTP基础上通过TLS/SSL加密传输，默认端口443，并通过证书验证服务器身份。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>参考答案供人工与AI批阅对照</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>编程基础</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1029,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1037,207 +1115,102 @@
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>列名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>题型</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>single单选 / multiple多选 / judge判断；short简答、fill填空为预留值，MVP暂不支持，遇到将跳过该行</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>题干</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>题目文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>选项A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>单选多选必填</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A选项文字（判断题可空）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>选项B</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>单选多选必填</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>B选项文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>选项C</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C选项文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>选项D</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>D选项文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>答案</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>如 A 或 ABD（多选用连续字母）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>解析</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>文字解析</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>难度</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>简单/中等/困难，默认中等</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>分数</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>整数，默认10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>题目分类名称；不存在自动新建；为空则归第一个分类</t>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>智题库 Excel 导入说明 (v1.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1. 本表(第一个工作表)为数据表，请勿修改表头顺序；导入时按表头名称匹配列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2. 支持题型: single(单选) / multiple(多选) / judge(判断) / fill(填空) / short(简答)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3. 答案列格式:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 单选/判断: 如 A 或 B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 多选: 如 A,B,C (直接连写 ABC 也可)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 填空: 一空多答用英文逗号分隔，多空用竖线分隔。例: 北京,北京市|京 (表示第一空填"北京"或"北京市"，第二空填"京")</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 填空题题干必须用三个下划线 ___ 表示空位，且空位数必须与答案竖线分段数一致，否则该行跳过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 简答: 答案列填标准答案全文；如需 AI 按点给分，可增加"踩分点"列，分号分隔。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4. 分类列: 逐题归入，分类不存在自动新建；留空则归入第一个题目分类。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5. 难度列支持: 简单/中等/困难 或 easy/medium/hard；分数列默认 10。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6. 无法解析的行会计入 skipped_count，不会中断整批导入。</t>
         </is>
       </c>
     </row>
